--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>לורן נוימן – בעולם הבא</v>
+        <v>אייל לוי – מדויק</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-03</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9c%d7%95%d7%a8%d7%9f-%d7%a0%d7%95%d7%99%d7%9e%d7%9f-%d7%91%d7%a2%d7%95%d7%9c%d7%9d-%d7%94%d7%91%d7%90/</v>
+        <v>https://yosmusic.com/%d7%90%d7%99%d7%99%d7%9c-%d7%9c%d7%95%d7%99-%d7%9e%d7%93%d7%95%d7%99%d7%a7/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "בעולם הבא” של לורן נוימן הוא שיר אבל אינטימי ושקט, כזה שאינו מתפרץ בכאב אלא מחזיק אותו בעדינות. המלנכוליה שבו אינה שוברת – היא מחזקת. במקום דרמה או זעקה, נוימן בוחרת בטון געגועים רך, כמעט לוחש, שמעניק למוות משמעות</v>
+        <v>השיר "מדויק” של כוכב הנוער והטיקטוק אייל לוי מייצג היטב את דור הפופ החדש,  שנולד קודם ברשתות החברתיות ורק אחר כך במוזיקה עצמה. זהו שיר שנבנה מראש לעולם של קליפים צעירים, ריקודי דאנס ואתגרי טיקטוק — ופחות להאזנה מסורתית לאלבום</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>לורן נוימן – בעולם הבא</v>
+        <v>אייל לוי – מדויק</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אייל לוי – מדויק</v>
+        <v>משה פרץ – יש על מי לסמוך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-03</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%99%d7%99%d7%9c-%d7%9c%d7%95%d7%99-%d7%9e%d7%93%d7%95%d7%99%d7%a7/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%a9%d7%94-%d7%a4%d7%a8%d7%a5-%d7%99%d7%a9-%d7%a2%d7%9c-%d7%9e%d7%99-%d7%9c%d7%a1%d7%9e%d7%95%d7%9a/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-03</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "מדויק” של כוכב הנוער והטיקטוק אייל לוי מייצג היטב את דור הפופ החדש,  שנולד קודם ברשתות החברתיות ורק אחר כך במוזיקה עצמה. זהו שיר שנבנה מראש לעולם של קליפים צעירים, ריקודי דאנס ואתגרי טיקטוק — ופחות להאזנה מסורתית לאלבום</v>
+        <v>השיר מציג שילוב בין שיר אמונה אישי לבין שיר הילולה קצבי המיועד לרחבת הריקודים. משה פרץ מנסה להחזיק שני עולמות במקביל: רוחניות פנימית לצד אנרגיה קהילתית חגיגית. לב השיר נמצא במשפט "לא הכל בידיים שלי / לא הכל צריך תשובה”.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אייל לוי – מדויק</v>
+        <v>משה פרץ – יש על מי לסמוך</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>משה פרץ – יש על מי לסמוך</v>
+        <v>יהונתן לוי להעריך</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-05</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%a9%d7%94-%d7%a4%d7%a8%d7%a5-%d7%99%d7%a9-%d7%a2%d7%9c-%d7%9e%d7%99-%d7%9c%d7%a1%d7%9e%d7%95%d7%9a/</v>
+        <v>https://yosmusic.com/%d7%99%d7%94%d7%95%d7%a0%d7%aa%d7%9f-%d7%9c%d7%95%d7%99-%d7%9c%d7%94%d7%a2%d7%a8%d7%99%d7%9a/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר מציג שילוב בין שיר אמונה אישי לבין שיר הילולה קצבי המיועד לרחבת הריקודים. משה פרץ מנסה להחזיק שני עולמות במקביל: רוחניות פנימית לצד אנרגיה קהילתית חגיגית. לב השיר נמצא במשפט "לא הכל בידיים שלי / לא הכל צריך תשובה”.</v>
+        <v>השיר “להעריך” של יהונתן לוי הוא בלדה איטית בעלת אופי רגשי, שנשענת על מסורת של שירה מזרחית עם סלסולים ומטען רוחני-אישי. מבחינת תוכן הוא שייך לז’אנר של שירי העצמה אישית ואמונה. הוא נכתב בשפה ישירה מאוד, כמעט דיבורית, ולכן נוצרת תחושה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>משה פרץ – יש על מי לסמוך</v>
+        <v>יהונתן לוי להעריך</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week01/titles.xlsx
@@ -436,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יהונתן לוי להעריך</v>
+        <v>יהונתן לוי – להעריך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-05</v>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יהונתן לוי להעריך</v>
+        <v>יהונתן לוי – להעריך</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יהונתן לוי – להעריך</v>
+        <v>רותם כהן – הייתי לבד</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-07</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%94%d7%95%d7%a0%d7%aa%d7%9f-%d7%9c%d7%95%d7%99-%d7%9c%d7%94%d7%a2%d7%a8%d7%99%d7%9a/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%aa%d7%9d-%d7%9b%d7%94%d7%9f-%d7%94%d7%99%d7%99%d7%aa%d7%99-%d7%9c%d7%91%d7%93/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר “להעריך” של יהונתן לוי הוא בלדה איטית בעלת אופי רגשי, שנשענת על מסורת של שירה מזרחית עם סלסולים ומטען רוחני-אישי. מבחינת תוכן הוא שייך לז’אנר של שירי העצמה אישית ואמונה. הוא נכתב בשפה ישירה מאוד, כמעט דיבורית, ולכן נוצרת תחושה</v>
+        <v>רותם כהן שר בלדת פופ אינטימית שמציגה משבר אישי דרך מסגרת רומנטית-מלנכולית. מדובר בשיר שנשען על נוסחה מוכרת בפופ הישראלי: סיפור של בדידות ומשבר פנימי שמגיע אל נקודת מפנה בזכות אהבה חדשה. הטקסט בנוי סביב שני צירים מרכזיים: וידוי על</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יהונתן לוי – להעריך</v>
+        <v>רותם כהן – הייתי לבד</v>
       </c>
     </row>
   </sheetData>
